--- a/artfynd/A 25625-2026 artfynd.xlsx
+++ b/artfynd/A 25625-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104465986</v>
+        <v>104465980</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622088.0490429311</v>
+        <v>622081</v>
       </c>
       <c r="R2" t="n">
-        <v>6893541.831223954</v>
+        <v>6893478</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104465984</v>
+        <v>104465981</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,7 +806,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621991.6852326707</v>
+        <v>622066</v>
       </c>
       <c r="R3" t="n">
-        <v>6893511.679150505</v>
+        <v>6893477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +848,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104465985</v>
+        <v>104465983</v>
       </c>
       <c r="B4" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,7 +907,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -951,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622034.2217767589</v>
+        <v>621994</v>
       </c>
       <c r="R4" t="n">
-        <v>6893540.352014185</v>
+        <v>6893495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +949,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104465991</v>
+        <v>104465984</v>
       </c>
       <c r="B5" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,7 +1008,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1067,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622110.4185571794</v>
+        <v>621991</v>
       </c>
       <c r="R5" t="n">
-        <v>6893519.248506538</v>
+        <v>6893512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,19 +1050,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,6 +1076,915 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104465985</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>622034</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6893540</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104465986</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>622088</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6893542</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104465987</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>622102</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6893515</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104465988</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>622110</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6893507</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104465989</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>622114</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6893510</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104465990</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>622104</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6893518</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104465991</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>622110</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6893519</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104465992</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>622114</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6893533</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104465993</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>622120</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6893534</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25625-2026 artfynd.xlsx
+++ b/artfynd/A 25625-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465980</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465981</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465983</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465984</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465985</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465986</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465987</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465988</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465989</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465990</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465991</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465992</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,8 +2050,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465993</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>